--- a/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59850</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>454</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29769</t>
+          <t>27106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>74852</t>
+          <t>74860</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49466</t>
+          <t>49274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>95085</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>123687</t>
+          <t>123126</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>21667</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>44645</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>373</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>486</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>30390</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>338</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>348</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>46243</t>
+          <t>46471</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>445</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9470,12 +9470,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>30367</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>42984</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>51921</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>69426</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>90250</t>
+          <t>90928</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>44712</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>54330</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>75498</t>
+          <t>76196</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>83163</t>
+          <t>83167</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>124185</t>
+          <t>123106</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>135498</t>
+          <t>135287</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -11610,12 +11610,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -11723,12 +11723,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>396</t>
         </is>
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -12175,12 +12175,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12190,82 +12190,82 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>6847</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr">
-        <is>
-          <t>6565</t>
-        </is>
-      </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P105" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q105" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R105" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="S105" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="T105" s="2" t="inlineStr">
-        <is>
-          <t>11313</t>
-        </is>
-      </c>
-      <c r="U105" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V105" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -12288,12 +12288,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12323,12 +12323,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12338,12 +12338,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12358,12 +12358,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -12401,12 +12401,12 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12451,12 +12451,12 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12514,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>21170</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12549,12 +12549,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12584,12 +12584,12 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>49281</t>
+          <t>48455</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12662,12 +12662,12 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>33649</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>63238</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -12677,12 +12677,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>68161</t>
+          <t>66697</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>103351</t>
+          <t>100708</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>237616</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="S110" s="2" t="inlineStr">
         <is>
-          <t>511856</t>
+          <t>510709</t>
         </is>
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>561089</t>
+          <t>560991</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
